--- a/Firmware/Modules/Ui/Ui_State_Machine.xlsx
+++ b/Firmware/Modules/Ui/Ui_State_Machine.xlsx
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -766,214 +766,241 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>۱</t>
+          <t>۰ (بالاترین)</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>اضافه‌ولتاژ ورودی</t>
+          <t>خطای فنی برد (سناریو ۷)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>ولتاژ ورودی بالای آستانهٔ ۷۰ با هیسترزیس ۷۱</t>
+          <t>FAULT_CHARGER_TECHNICAL قفل است</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>قرمز چشمک‌زن + سبز روشن</t>
+          <t>هر سه LED با فاز مشترک هم‌زمان</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>بوق دوره‌ای (۴۰ تا ۴۳)</t>
+          <t>بوق مستقل ۱۳۷ تا ۱۴۰</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>۲</t>
+          <t>۱</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>قطع باتری</t>
+          <t>اضافه‌ولتاژ ورودی</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>بیت FAULT_CHARGER_BAT_LOST قفل است</t>
+          <t>ولتاژ ورودی بالای آستانهٔ ۷۰ با هیسترزیس ۷۱</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>چهرهٔ قطع باتری</t>
+          <t>قرمز چشمک‌زن + سبز روشن</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>سه بوق کوتاه (۴۷ تا ۴۹)</t>
+          <t>بوق دوره‌ای (۴۰ تا ۴۳)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>۳</t>
+          <t>۲</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>باتری خراب (سناریو ۶)</t>
+          <t>قطع باتری</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>حکم مهلت شارژ قفل شده</t>
+          <t>بیت FAULT_CHARGER_BAT_LOST قفل است</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>قرمز ثابت (پیش‌فرض ۱۳۰ = ۰)</t>
+          <t>چهرهٔ قطع باتری</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>بوق هر ۱۲۸ به طول ۱۲۹</t>
+          <t>سه بوق کوتاه (۴۷ تا ۴۹)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
+          <t>۳</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>باتری خراب (سناریو ۶)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>حکم مهلت شارژ قفل شده</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>قرمز ثابت (پیش‌فرض ۱۳۰ = ۰)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>بوق هر ۱۲۸ به طول ۱۲۹</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
           <t>۴</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>عدم‌توازن (سناریو ۵)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن (۱۲۳ و ۱۲۴)</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>بوق هر ۱۱۵ به طول ۱۱۶</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>۵</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>شارژ کامل</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>اعلام اتمام شارژ یا قفل ولتاژی ۱۰۰/۹۵</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>سبز ثابت</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>بی‌صدا</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>۵</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>شارژ کامل</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>اعلام اتمام شارژ یا قفل ولتاژی ۱۰۰/۹۵</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>سبز ثابت</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>بی‌صدا</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>۶</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ورودی سالم بدون شارژ</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>ورودی هست ولی هیچ کانالی پمپ نمی‌کند</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>بی‌صدا</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>۷</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>در حال شارژ</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>ورودی هست و کانالی فعال است</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>سبز ثابت + زرد چشمک‌زن متناسب با درصد</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>بی‌صدا</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>۸</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>کار روی باتری (دشارژ)</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>ورودی قطع است</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>سبز چشمک‌زن متناسب با درصد</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>باندهای بوق ۱ تا ۳ و باند بحرانی</t>
         </is>

--- a/Firmware/Modules/Ui/Ui_State_Machine.xlsx
+++ b/Firmware/Modules/Ui/Ui_State_Machine.xlsx
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -531,7 +531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -688,7 +688,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1017,7 +1017,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/Ui/Ui_State_Machine.xlsx
+++ b/Firmware/Modules/Ui/Ui_State_Machine.xlsx
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -899,29 +899,29 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>۵</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>شارژ کامل</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>اعلام اتمام شارژ یا قفل ولتاژی ۱۰۰/۹۵</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>سبز ثابت</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>بی‌صدا</t>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>باتری ضعیف (سناریو ۸)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف قفل است</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>قرمز چشمک‌زن با دورهٔ ۱۵۱ و سهم ۱۵۲ (سبز و زرد خاموش)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>بوق مستقل ۱۵۳..۱۵۶</t>
         </is>
       </c>
     </row>
@@ -933,74 +933,101 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>شارژ کامل</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>اعلام اتمام شارژ یا قفل ولتاژی ۱۰۰/۹۵</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>سبز ثابت</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>بی‌صدا</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>۷</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
           <t>ورودی سالم بدون شارژ</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>ورودی هست ولی هیچ کانالی پمپ نمی‌کند</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>بی‌صدا</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>۷</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>۸</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>در حال شارژ</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>ورودی هست و کانالی فعال است</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>سبز ثابت + زرد چشمک‌زن متناسب با درصد</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>بی‌صدا</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>۸</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>۹</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>کار روی باتری (دشارژ)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>ورودی قطع است</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>سبز چشمک‌زن متناسب با درصد</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>باندهای بوق ۱ تا ۳ و باند بحرانی</t>
         </is>

--- a/Firmware/Modules/Ui/Ui_State_Machine.xlsx
+++ b/Firmware/Modules/Ui/Ui_State_Machine.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ سناریوها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ باندهای دشارژ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ سناریوها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ باندهای دشارژ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -906,12 +906,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>باتری ضعیف (سناریو ۸)</t>
+          <t>باتری فرسوده (سناریو ۸)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>حکم باتری ضعیف قفل است</t>
+          <t>حکم قفل است و برق ورودی نیست</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -926,27 +926,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>۶</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>شارژ کامل</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>اعلام اتمام شارژ یا قفل ولتاژی ۱۰۰/۹۵</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>سبز ثابت</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>۵ب</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>مسیر باتری بسته + بدون برق ورودی</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ولتاژ پایین قطع کرده یا سقف تلاش تمام شده</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>هر سه چراغ خاموش</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>بی‌صدا</t>
         </is>
@@ -955,79 +955,106 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>۶</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>شارژ کامل</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>اعلام اتمام شارژ یا قفل ولتاژی ۱۰۰/۹۵</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>سبز ثابت</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>بی‌صدا</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>۷</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>ورودی سالم بدون شارژ</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>ورودی هست ولی هیچ کانالی پمپ نمی‌کند</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>بی‌صدا</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>۸</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>در حال شارژ</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>ورودی هست و کانالی فعال است</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>سبز ثابت + زرد چشمک‌زن متناسب با درصد</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>بی‌صدا</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>۹</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>کار روی باتری (دشارژ)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>ورودی قطع است</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>سبز چشمک‌زن متناسب با درصد</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>باندهای بوق ۱ تا ۳ و باند بحرانی</t>
         </is>

--- a/Firmware/Modules/Ui/Ui_State_Machine.xlsx
+++ b/Firmware/Modules/Ui/Ui_State_Machine.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ سناریوها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ باندهای دشارژ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="۱ سناریوها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="۲ باندهای دشارژ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>ورودی هست ولی هیچ کانالی پمپ نمی‌کند</t>
+          <t>مجوز مشترک ورودی Fault درست است ولی هیچ کانالی پمپ نمی‌کند</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>ورودی هست و کانالی فعال است</t>
+          <t>مجوز مشترک ورودی Fault درست است و کانالی فعال است</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>ورودی قطع است</t>
+          <t>مجوز مشترک ورودی Fault قطع است (بیرون ۳۳/۳۴ یا هنوز مسلح‌نشده با ۱۶۹/۱۷۰)</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">

--- a/Firmware/Modules/Ui/Ui_State_Machine.xlsx
+++ b/Firmware/Modules/Ui/Ui_State_Machine.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>ولتاژ ورودی بالای آستانهٔ ۷۰ با هیسترزیس ۷۱</t>
+          <t>ولتاژ ورودی بالای سقف مشترک q34 با هیسترزیس q71 (q70 آینهٔ فقط‌خواندنی)</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">

--- a/Firmware/Modules/Ui/Ui_State_Machine.xlsx
+++ b/Firmware/Modules/Ui/Ui_State_Machine.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ سناریوها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ باندهای دشارژ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ سناریوها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ باندهای دشارژ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
